--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2267,8 +2389,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:S14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2289,751 +2415,624 @@
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">몽금포 타령 — 민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">몽금포 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無
 南</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">북</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">장산</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="K4" s="17"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">곳</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="P5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">겠네</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="S6" s="16"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="17"/>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="17"/>
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="20"/>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="P7" s="14"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="18"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="16"/>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="16"/>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="19"/>
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="16"/>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="19"/>
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:S2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="67"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I49" s="3"/>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―○</t>
+          <t xml:space="preserve">–○</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―○</t>
+          <t xml:space="preserve">–○</t>
         </is>
       </c>
       <c r="I55" s="3"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I7" s="12"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O7" s="9"/>
@@ -4710,7 +4710,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―○</t>
+          <t xml:space="preserve">–○</t>
         </is>
       </c>
       <c r="I14" s="13"/>

--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3966,101 +4007,101 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">몽금포 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">북</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -4068,78 +4109,78 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">레</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4147,78 +4188,78 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">곳</t>
         </is>
@@ -4226,78 +4267,78 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N6" s="18" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
@@ -4305,184 +4346,184 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="23"/>
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="25"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">레</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="23"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="26"/>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="I8" s="26"/>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">게</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="18" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M8" s="28"/>
+      <c r="N8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌仲</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q8" s="13"/>
+      <c r="Q8" s="28"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G9" s="27"/>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K9" s="22"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4490,54 +4531,54 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="C10" s="25"/>
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4545,199 +4586,199 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="28"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="I11" s="28"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K11" s="26"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="Q11" s="13"/>
+      <c r="Q11" s="28"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="C12" s="27"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K12" s="27"/>
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="M12" s="27"/>
+      <c r="N12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P12" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q12" s="11"/>
+      <c r="P12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q12" s="27"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="9"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="C14" s="28"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G14" s="28"/>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–○</t>
         </is>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="I14" s="28"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M14" s="28"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="10"/>
+      <c r="O14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -3984,28 +3984,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4398,12 +4398,12 @@
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Q8" s="28"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="24" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="24" t="inlineStr">
         <is>
@@ -4551,13 +4551,13 @@
       <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="23"/>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="24" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       <c r="E11" s="28"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="26"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q11" s="28"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="24" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Q12" s="27"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="24" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="24" t="inlineStr">
         <is>

--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -2649,12 +2649,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="3"/>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I89" s="3"/>
@@ -4737,7 +4737,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" s="28"/>
@@ -4751,7 +4751,7 @@
       <c r="G14" s="28"/>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="28"/>

--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4035,13 +4058,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4051,7 +4074,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4061,7 +4084,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4071,7 +4094,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4081,7 +4104,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -4091,7 +4114,7 @@
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">북</t>
         </is>
@@ -4101,7 +4124,7 @@
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -4114,13 +4137,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
@@ -4130,7 +4153,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">레</t>
         </is>
@@ -4140,7 +4163,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
@@ -4150,7 +4173,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
@@ -4160,7 +4183,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -4170,7 +4193,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="23" t="inlineStr">
+      <c r="O4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -4180,7 +4203,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="23" t="inlineStr">
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4193,13 +4216,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4209,7 +4232,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4219,7 +4242,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4229,7 +4252,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4239,7 +4262,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4249,7 +4272,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4259,7 +4282,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">곳</t>
         </is>
@@ -4272,13 +4295,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
@@ -4288,7 +4311,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4298,7 +4321,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
@@ -4308,7 +4331,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
@@ -4318,7 +4341,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -4328,7 +4351,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4338,7 +4361,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
@@ -4351,19 +4374,19 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">레</t>
         </is>
@@ -4373,19 +4396,19 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
@@ -4395,13 +4418,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="30"/>
     </row>
     <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
@@ -4410,19 +4433,19 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4432,13 +4455,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="K8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">게</t>
         </is>
@@ -4448,13 +4471,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="28"/>
+      <c r="M8" s="34"/>
       <c r="N8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌仲</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="O8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
@@ -4464,7 +4487,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q8" s="28"/>
+      <c r="Q8" s="34"/>
     </row>
     <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
@@ -4473,25 +4496,25 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="27"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4501,19 +4524,19 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="22"/>
+      <c r="K9" s="29"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="29"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4523,7 +4546,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4536,39 +4559,39 @@
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="30"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="30"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="23"/>
+      <c r="M10" s="30"/>
       <c r="N10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4578,7 +4601,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="inlineStr">
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4591,41 +4614,41 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E11" s="28"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="I11" s="28"/>
+      <c r="I11" s="34"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="21"/>
-      <c r="M11" s="26"/>
+      <c r="M11" s="32"/>
       <c r="N11" s="21"/>
-      <c r="O11" s="26"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="34"/>
     </row>
     <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
@@ -4634,19 +4657,19 @@
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="C12" s="27"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4656,7 +4679,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4666,19 +4689,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="27"/>
+      <c r="K12" s="33"/>
       <c r="L12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="M12" s="27"/>
+      <c r="M12" s="33"/>
       <c r="N12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="O12" s="27" t="inlineStr">
+      <c r="O12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4688,7 +4711,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="27"/>
+      <c r="Q12" s="33"/>
     </row>
     <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
@@ -4697,41 +4720,41 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="23"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="O13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="P13" s="21"/>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="30"/>
     </row>
     <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
@@ -4740,45 +4763,45 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="21"/>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="28"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="28"/>
+      <c r="M14" s="34"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="O14" s="26" t="inlineStr">
+      <c r="O14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="P14" s="21"/>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,10 +218,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
@@ -235,28 +233,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +336,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">88</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
     </row>
@@ -365,7 +348,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -377,7 +360,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -401,7 +384,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 43%</t>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
         </is>
       </c>
     </row>
@@ -429,7 +412,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목줄 "몽금포 타령  굿거리  (서도소리)". 12정간, 굵은 선 3칸마다. 손그림 격자(번호 없음). 각 율명 줄 오른쪽에 가사 칸. 8줄 사용, 오른쪽 1. 오른쪽 위 여백에 "왜 각하리" 비슷한 메모(판독 불확실). 여러 칸에 덧칠/겹쳐쓴(無南 등) 교정 흔적 있음→비고. 하단 가사칸 요성 물결선(멜리스마)은 비고로 남김. AI 재판독 초안(독립 검수).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "몽금포 타령  굿거리 (서도소리)". 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 선 3칸마다 → 3/4·12. 격자 오른쪽 끝 2줄은 비어 있고(맨 오른쪽 위 여백에 "※ 요성 격하게" 메모) 그 왼쪽부터 율명 6줄 → 줄1="장산곳" 줄. 가사는 각 율명 줄 오른쪽 칸. 한 장 한 곡.</t>
         </is>
       </c>
     </row>
@@ -615,22 +598,26 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="J2" s="4"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氵가 사선 하나로 흘려 씀</t>
+        </is>
+      </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -732,22 +719,26 @@
       <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">더</t>
-        </is>
-      </c>
-      <c r="J5" s="4"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">머</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 머/마?</t>
+        </is>
+      </c>
       <c r="K5" s="2"/>
     </row>
     <row r="6">
@@ -806,22 +797,23 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵仲</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳|㳞</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">루</t>
+        </is>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -847,12 +839,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -886,19 +878,15 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I9" s="2"/>
       <c r="J9" s="4"/>
       <c r="K9" s="2"/>
     </row>
@@ -923,22 +911,23 @@
       <c r="F10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|潢</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11">
@@ -962,22 +951,22 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 가사칸에 요성 물결선(멜리스마)</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -1003,12 +992,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1042,12 +1031,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1081,12 +1070,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1118,26 +1107,22 @@
       <c r="F15" s="2">
         <v>2</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 나? 확실치 않음</t>
-        </is>
-      </c>
+      <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16">
@@ -1156,22 +1141,27 @@
         <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">湳|㳞</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
+          <t xml:space="preserve">湳
+㳞</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">더</t>
+        </is>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1191,31 +1181,27 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌仲</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌仲</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">더</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌(氵姑)+仲 나란히</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1234,26 +1220,23 @@
         <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" s="2">
         <v>3</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|潢</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I18" s="2"/>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1273,31 +1256,23 @@
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵姑</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1316,31 +1291,24 @@
         <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
     <row r="21">
@@ -1359,26 +1327,22 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I21" s="2"/>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1392,30 +1356,30 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">금</t>
         </is>
       </c>
       <c r="J22" s="4"/>
@@ -1437,24 +1401,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금</t>
+          <t xml:space="preserve">일</t>
         </is>
       </c>
       <c r="J23" s="4"/>
@@ -1476,24 +1441,24 @@
         <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일</t>
+          <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="J24" s="4"/>
@@ -1515,24 +1480,24 @@
         <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="J25" s="4"/>
@@ -1554,27 +1519,27 @@
         <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="J26" s="4"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸에 ㅣ(늘임)만</t>
+        </is>
+      </c>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1593,19 +1558,19 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="2">
         <v>2</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1632,27 +1597,28 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|潢</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1671,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="2">
         <v>3</v>
@@ -1706,27 +1672,23 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2">
-        <v>4</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1745,27 +1707,23 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I31" s="3"/>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
     <row r="32">
@@ -1784,27 +1742,24 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|潢</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1817,32 +1772,28 @@
         </is>
       </c>
       <c r="C33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I33" s="2"/>
       <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
@@ -1862,31 +1813,27 @@
         <v>4</v>
       </c>
       <c r="E34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맏</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 맏/만?</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
     <row r="35">
@@ -1905,7 +1852,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
@@ -1922,7 +1869,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나</t>
+          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="J35" s="4"/>
@@ -1944,24 +1891,24 @@
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J36" s="4"/>
@@ -1983,22 +1930,26 @@
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
         <v>2</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보</t>
+        </is>
+      </c>
       <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
@@ -2018,31 +1969,24 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
         <v>2</v>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">게</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃, 가사 게/겠?</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|無</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -2061,22 +2005,26 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I39" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겠</t>
+        </is>
+      </c>
       <c r="J39" s="4"/>
       <c r="K39" s="2"/>
     </row>
@@ -2096,22 +2044,26 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2">
         <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
       <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
@@ -2131,19 +2083,19 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
         <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2166,27 +2118,25 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" s="2">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">덧칠(검게 지운 흔적)</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2205,27 +2155,23 @@
         <v>4</v>
       </c>
       <c r="E43" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2">
         <v>4</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘, 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
     <row r="44">
@@ -2244,19 +2190,19 @@
         <v>4</v>
       </c>
       <c r="E44" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2">
         <v>4</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2273,32 +2219,29 @@
         </is>
       </c>
       <c r="C45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I45" s="2"/>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2318,24 +2261,24 @@
         <v>5</v>
       </c>
       <c r="E46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">맏</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J46" s="4"/>
@@ -2357,27 +2300,32 @@
         <v>5</v>
       </c>
       <c r="E47" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="J47" s="4"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南無 둘레에 동그라미 표시</t>
+        </is>
+      </c>
       <c r="K47" s="2"/>
     </row>
     <row r="48">
@@ -2396,31 +2344,27 @@
         <v>5</v>
       </c>
       <c r="E48" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
     <row r="49">
@@ -2439,27 +2383,27 @@
         <v>5</v>
       </c>
       <c r="E49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">短橫線(연음)+無</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50">
@@ -2478,22 +2422,27 @@
         <v>5</v>
       </c>
       <c r="E50" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F50" s="2">
         <v>2</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I50" s="2"/>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
       <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
@@ -2513,10 +2462,10 @@
         <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F51" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -2530,7 +2479,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2552,22 +2501,26 @@
         <v>5</v>
       </c>
       <c r="E52" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" s="2">
         <v>3</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I52" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
@@ -2587,27 +2540,27 @@
         <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" s="2">
         <v>3</v>
       </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I53" s="3"/>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J53" s="4"/>
       <c r="K53" s="2"/>
     </row>
     <row r="54">
@@ -2626,26 +2579,22 @@
         <v>5</v>
       </c>
       <c r="E54" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F54" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I54" s="2"/>
       <c r="J54" s="4"/>
       <c r="K54" s="2"/>
     </row>
@@ -2665,27 +2614,27 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F55" s="2">
         <v>4</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">短橫線+○</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
     <row r="56">
@@ -2698,32 +2647,29 @@
         </is>
       </c>
       <c r="C56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F56" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">㳞|潢</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I56" s="2"/>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2737,35 +2683,32 @@
         </is>
       </c>
       <c r="C57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">潢|△</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">레</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢
+△</t>
+        </is>
+      </c>
+      <c r="I57" s="3"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">동그라미로 묶어 교정</t>
+          <t xml:space="preserve">潢 아래 작은 △(○?)</t>
         </is>
       </c>
       <c r="K57" s="2"/>
@@ -2786,24 +2729,24 @@
         <v>6</v>
       </c>
       <c r="E58" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">야</t>
+          <t xml:space="preserve">님</t>
         </is>
       </c>
       <c r="J58" s="4"/>
@@ -2825,24 +2768,24 @@
         <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="J59" s="4"/>
@@ -2864,24 +2807,24 @@
         <v>6</v>
       </c>
       <c r="E60" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">레</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J60" s="4"/>
@@ -2903,24 +2846,24 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" s="2">
         <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">야</t>
+          <t xml:space="preserve">보</t>
         </is>
       </c>
       <c r="J61" s="4"/>
@@ -2942,27 +2885,24 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F62" s="2">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I62" s="3"/>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|無</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="4"/>
       <c r="K62" s="2"/>
     </row>
     <row r="63">
@@ -2981,27 +2921,27 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F63" s="2">
-        <v>3</v>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I63" s="3"/>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겠</t>
+        </is>
+      </c>
+      <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
     <row r="64">
@@ -3020,22 +2960,26 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F64" s="2">
         <v>3</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I64" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -3055,32 +2999,32 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2">
-        <v>4</v>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="I65" s="5"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K65" s="2"/>
+          <t xml:space="preserve">검게 덧칠해 지움</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
@@ -3098,27 +3042,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" s="2">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I66" s="3"/>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
     <row r="67">
@@ -3137,869 +3079,27 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
       </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I67" s="3"/>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃, 아래 ○</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68">
-      <c r="A68" s="2">
-        <v>1</v>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C68" s="2">
-        <v>7</v>
-      </c>
-      <c r="D68" s="2">
-        <v>7</v>
-      </c>
-      <c r="E68" s="2">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2">
-        <v>1</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님</t>
-        </is>
-      </c>
-      <c r="J68" s="4"/>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2">
-        <v>1</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C69" s="2">
-        <v>7</v>
-      </c>
-      <c r="D69" s="2">
-        <v>7</v>
-      </c>
-      <c r="E69" s="2">
-        <v>2</v>
-      </c>
-      <c r="F69" s="2">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맏</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2">
-        <v>1</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C70" s="2">
-        <v>7</v>
-      </c>
-      <c r="D70" s="2">
-        <v>7</v>
-      </c>
-      <c r="E70" s="2">
-        <v>3</v>
-      </c>
-      <c r="F70" s="2">
-        <v>1</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="J70" s="4"/>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>1</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C71" s="2">
-        <v>7</v>
-      </c>
-      <c r="D71" s="2">
-        <v>7</v>
-      </c>
-      <c r="E71" s="2">
-        <v>4</v>
-      </c>
-      <c r="F71" s="2">
-        <v>2</v>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>1</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C72" s="2">
-        <v>7</v>
-      </c>
-      <c r="D72" s="2">
-        <v>7</v>
-      </c>
-      <c r="E72" s="2">
-        <v>5</v>
-      </c>
-      <c r="F72" s="2">
-        <v>2</v>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I72" s="3"/>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>1</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C73" s="2">
-        <v>7</v>
-      </c>
-      <c r="D73" s="2">
-        <v>7</v>
-      </c>
-      <c r="E73" s="2">
-        <v>6</v>
-      </c>
-      <c r="F73" s="2">
-        <v>2</v>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I73" s="3"/>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>1</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C74" s="2">
-        <v>7</v>
-      </c>
-      <c r="D74" s="2">
-        <v>7</v>
-      </c>
-      <c r="E74" s="2">
-        <v>7</v>
-      </c>
-      <c r="F74" s="2">
-        <v>3</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I74" s="2"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2">
-        <v>1</v>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C75" s="2">
-        <v>7</v>
-      </c>
-      <c r="D75" s="2">
-        <v>7</v>
-      </c>
-      <c r="E75" s="2">
-        <v>8</v>
-      </c>
-      <c r="F75" s="2">
-        <v>3</v>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I75" s="3"/>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">덧칠로 검게(쉼/지움?)</t>
-        </is>
-      </c>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2">
-        <v>1</v>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C76" s="2">
-        <v>7</v>
-      </c>
-      <c r="D76" s="2">
-        <v>7</v>
-      </c>
-      <c r="E76" s="2">
-        <v>9</v>
-      </c>
-      <c r="F76" s="2">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I76" s="3"/>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2">
-        <v>1</v>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C77" s="2">
-        <v>7</v>
-      </c>
-      <c r="D77" s="2">
-        <v>7</v>
-      </c>
-      <c r="E77" s="2">
-        <v>10</v>
-      </c>
-      <c r="F77" s="2">
-        <v>4</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I77" s="2"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2">
-        <v>1</v>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C78" s="2">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2">
-        <v>8</v>
-      </c>
-      <c r="E78" s="2">
-        <v>1</v>
-      </c>
-      <c r="F78" s="2">
-        <v>1</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I78" s="2"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2">
-        <v>1</v>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C79" s="2">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2">
-        <v>8</v>
-      </c>
-      <c r="E79" s="2">
-        <v>2</v>
-      </c>
-      <c r="F79" s="2">
-        <v>1</v>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I79" s="2"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2">
-        <v>1</v>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C80" s="2">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2">
-        <v>8</v>
-      </c>
-      <c r="E80" s="2">
-        <v>3</v>
-      </c>
-      <c r="F80" s="2">
-        <v>1</v>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I80" s="2"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2">
-        <v>1</v>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C81" s="2">
-        <v>8</v>
-      </c>
-      <c r="D81" s="2">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2">
-        <v>4</v>
-      </c>
-      <c r="F81" s="2">
-        <v>2</v>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2">
-        <v>1</v>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C82" s="2">
-        <v>8</v>
-      </c>
-      <c r="D82" s="2">
-        <v>8</v>
-      </c>
-      <c r="E82" s="2">
-        <v>5</v>
-      </c>
-      <c r="F82" s="2">
-        <v>2</v>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I82" s="2"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2">
-        <v>1</v>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C83" s="2">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2">
-        <v>8</v>
-      </c>
-      <c r="E83" s="2">
-        <v>6</v>
-      </c>
-      <c r="F83" s="2">
-        <v>2</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I83" s="2"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>1</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C84" s="2">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2">
-        <v>7</v>
-      </c>
-      <c r="F84" s="2">
-        <v>3</v>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I84" s="3"/>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2">
-        <v>1</v>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C85" s="2">
-        <v>8</v>
-      </c>
-      <c r="D85" s="2">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2">
-        <v>8</v>
-      </c>
-      <c r="F85" s="2">
-        <v>3</v>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I85" s="3"/>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2">
-        <v>1</v>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C86" s="2">
-        <v>8</v>
-      </c>
-      <c r="D86" s="2">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2">
-        <v>9</v>
-      </c>
-      <c r="F86" s="2">
-        <v>3</v>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2">
-        <v>1</v>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C87" s="2">
-        <v>8</v>
-      </c>
-      <c r="D87" s="2">
-        <v>8</v>
-      </c>
-      <c r="E87" s="2">
-        <v>10</v>
-      </c>
-      <c r="F87" s="2">
-        <v>4</v>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="I87" s="3"/>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2">
-        <v>1</v>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C88" s="2">
-        <v>8</v>
-      </c>
-      <c r="D88" s="2">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2">
-        <v>11</v>
-      </c>
-      <c r="F88" s="2">
-        <v>4</v>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I88" s="3"/>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>1</v>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/몽금포 타령.png</t>
-        </is>
-      </c>
-      <c r="C89" s="2">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2">
-        <v>12</v>
-      </c>
-      <c r="F89" s="2">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I89" s="3"/>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 작은 ○</t>
-        </is>
-      </c>
-      <c r="K89" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K89"/>
+  <autoFilter ref="A1:K67"/>
 </worksheet>
 </file>
 
@@ -4019,16 +3119,12 @@
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4046,769 +3142,640 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-    </row>
-    <row r="3" ht="29.14" customHeight="1">
+    </row>
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님</t>
+        </is>
+      </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님</t>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="O3" s="29" t="inlineStr">
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">북</t>
         </is>
       </c>
-      <c r="P3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="Q3" s="29" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="29.14" customHeight="1">
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맏</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">레</t>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맏</t>
-        </is>
-      </c>
-      <c r="J4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맏</t>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="M4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일</t>
-        </is>
-      </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="30" t="inlineStr">
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="29.14" customHeight="1">
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="32"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곳</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곳</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="29.14" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">더</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="29.14" customHeight="1">
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">머</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="77.61" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="G7" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">레</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K7" s="30"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M7" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O7" s="30"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q7" s="30"/>
-    </row>
-    <row r="8" ht="29.14" customHeight="1">
+      <c r="M7" s="25"/>
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E8" s="34"/>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겠</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겠</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞</t>
+        </is>
+      </c>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">더</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞</t>
+        </is>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">루</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="77.61" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="77.61" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M10" s="25"/>
+    </row>
+    <row r="11" ht="77.61" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="M11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="77.61" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="32"/>
-      <c r="J8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">게</t>
-        </is>
-      </c>
-      <c r="L8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M8" s="34"/>
-      <c r="N8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌仲</t>
-        </is>
-      </c>
-      <c r="O8" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">더</t>
-        </is>
-      </c>
-      <c r="P8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q8" s="34"/>
-    </row>
-    <row r="9" ht="29.14" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="77.61" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="25"/>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+△</t>
+        </is>
+      </c>
+      <c r="E14" s="30"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="29.14" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="29.14" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="Q11" s="34"/>
-    </row>
-    <row r="12" ht="29.14" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="33"/>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="M12" s="33"/>
-      <c r="N12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="O12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="P12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q12" s="33"/>
-    </row>
-    <row r="13" ht="29.14" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌潢</t>
-        </is>
-      </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O13" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="30"/>
-    </row>
-    <row r="14" ht="29.14" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M14" s="34"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南</t>
-        </is>
-      </c>
-      <c r="O14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="32"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B2:M2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -461,10 +461,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/몽금포 타령.xlsx
+++ b/sheets/민요/검수/몽금포 타령.xlsx
@@ -3038,17 +3038,17 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="9" width="6"/>
   </cols>
   <sheetData>
